--- a/daily_smoke_test/autopts_report/report_2026_03_26_01_07_29.xlsx
+++ b/daily_smoke_test/autopts_report/report_2026_03_26_01_07_29.xlsx
@@ -14,9 +14,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="292">
-  <si>
-    <t>AutoPTS Report: 2026-03-26 01:41</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="237">
+  <si>
+    <t>AutoPTS Report: 2026-03-26 01:47</t>
   </si>
   <si>
     <t>Test Case</t>
@@ -49,9 +49,6 @@
     <t>PASS</t>
   </si>
   <si>
-    <t>AICS_SR_CP_BV_01_C_2026_03_26_01_19_19.xml</t>
-  </si>
-  <si>
     <t>Audio Input Control Point - Set Gain Setting</t>
   </si>
   <si>
@@ -64,9 +61,6 @@
     <t>ASCS/SR/ACP/BV-01-C</t>
   </si>
   <si>
-    <t>ASCS_SR_ACP_BV_01_C_2026_03_26_01_20_51.xml</t>
-  </si>
-  <si>
     <t>Config Codec in Idle State - Server is Audio Sink</t>
   </si>
   <si>
@@ -79,9 +73,6 @@
     <t>BAP/BA/BASS/BV-02-C</t>
   </si>
   <si>
-    <t>BAP_BA_BASS_BV_02_C_2026_03_26_01_23_33.xml</t>
-  </si>
-  <si>
     <t>Initiate Remote Scan Start Operation</t>
   </si>
   <si>
@@ -94,9 +85,6 @@
     <t>BAP/BSNK/SCC/BV-04-C</t>
   </si>
   <si>
-    <t>BAP_BSNK_SCC_BV_04_C_2026_03_26_01_23_16.xml</t>
-  </si>
-  <si>
     <t>Sync to PA, LC3 16_2_1</t>
   </si>
   <si>
@@ -109,9 +97,6 @@
     <t>BAP/BSRC/SCC/BV-01-C</t>
   </si>
   <si>
-    <t>BAP_BSRC_SCC_BV_01_C_2026_03_26_01_22_57.xml</t>
-  </si>
-  <si>
     <t>Config Broadcast, LC3 8_1_1</t>
   </si>
   <si>
@@ -124,9 +109,6 @@
     <t>BAP/CL/CGGIT/CHA/BV-01-C</t>
   </si>
   <si>
-    <t>BAP_CL_CGGIT_CHA_BV_01_C_2026_03_26_01_21_20.xml</t>
-  </si>
-  <si>
     <t>Characteristic GGIT - Sink PAC</t>
   </si>
   <si>
@@ -139,9 +121,6 @@
     <t>BAP/UCL/SCC/BV-110-C</t>
   </si>
   <si>
-    <t>BAP_UCL_SCC_BV_110_C_2026_03_26_01_21_45.xml</t>
-  </si>
-  <si>
     <t>UCL SNK Release in Enabling state</t>
   </si>
   <si>
@@ -154,9 +133,6 @@
     <t>BAP/USR/DISC/BV-01-C</t>
   </si>
   <si>
-    <t>BAP_USR_DISC_BV_01_C_2026_03_26_01_22_33.xml</t>
-  </si>
-  <si>
     <t>Expose Audio Sink Capabilities</t>
   </si>
   <si>
@@ -169,9 +145,6 @@
     <t>BASS/SR/CP/BV-01-C</t>
   </si>
   <si>
-    <t>BASS_SR_CP_BV_01_C_2026_03_26_01_24_07.xml</t>
-  </si>
-  <si>
     <t>Remote Scan Stopped</t>
   </si>
   <si>
@@ -184,9 +157,6 @@
     <t>CAP/COM/CRC/BV-01-C</t>
   </si>
   <si>
-    <t>CAP_COM_CRC_BV_01_C_2026_03_26_01_25_59.xml</t>
-  </si>
-  <si>
     <t>Change Volume - Set Absolute Volume - Multiple Devices</t>
   </si>
   <si>
@@ -199,9 +169,6 @@
     <t>CAP/INI/BST/BV-01-C</t>
   </si>
   <si>
-    <t>CAP_INI_BST_BV_01_C_2026_03_26_01_25_38.xml</t>
-  </si>
-  <si>
     <t>Broadcast Audio Starting for Single Audio Stream</t>
   </si>
   <si>
@@ -214,9 +181,6 @@
     <t>CAP/INI/UST/BV-01-C</t>
   </si>
   <si>
-    <t>CAP_INI_UST_BV_01_C_2026_03_26_01_24_32.xml</t>
-  </si>
-  <si>
     <t>Unicast Audio Starting Unidirectional Audio to a Sink - No CCID</t>
   </si>
   <si>
@@ -229,9 +193,6 @@
     <t>CCP/CL/CGGIT/CHA/BV-01-C</t>
   </si>
   <si>
-    <t>CCP_CL_CGGIT_CHA_BV_01_C_2026_03_26_01_26_38.xml</t>
-  </si>
-  <si>
     <t>Characteristic GGIT - Bearer Provider Name</t>
   </si>
   <si>
@@ -244,9 +205,6 @@
     <t>CSIP/CL/CGGIT/CHA/BV-01-C</t>
   </si>
   <si>
-    <t>CSIP_CL_CGGIT_CHA_BV_01_C_2026_03_26_01_18_39.xml</t>
-  </si>
-  <si>
     <t>Characteristic GGIT - Set Identity Resolving Key</t>
   </si>
   <si>
@@ -259,9 +217,6 @@
     <t>CSIS/SR/SGGIT/CHA/BV-03-C</t>
   </si>
   <si>
-    <t>CSIS_SR_SGGIT_CHA_BV_03_C_2026_03_26_01_27_21.xml</t>
-  </si>
-  <si>
     <t>Characteristic GGIT - Set Member Lock</t>
   </si>
   <si>
@@ -274,9 +229,6 @@
     <t>DFUM/CL/FU/BV-01-C</t>
   </si>
   <si>
-    <t>DFUM_CL_FU_BV_01_C_2026_03_26_01_36_19.xml</t>
-  </si>
-  <si>
     <t>Firmware Compatibility Check Procedure, IUT as Initiator</t>
   </si>
   <si>
@@ -289,9 +241,6 @@
     <t>DFUM/SR/FD/BV-01-C</t>
   </si>
   <si>
-    <t>DFUM_SR_FD_BV_01_C_2026_03_26_01_36_56.xml</t>
-  </si>
-  <si>
     <t>Receive Firmware Distribution Capabilities Get</t>
   </si>
   <si>
@@ -304,9 +253,6 @@
     <t>DIS/SR/SGGIT/CHA/BV-01-C</t>
   </si>
   <si>
-    <t>DIS_SR_SGGIT_CHA_BV_01_C_2026_03_26_01_08_49.xml</t>
-  </si>
-  <si>
     <t>Characteristic GGIT - Manufacturer Name String</t>
   </si>
   <si>
@@ -319,9 +265,6 @@
     <t>GAP/BROB/OBSV/BV-02-C</t>
   </si>
   <si>
-    <t>GAP_BROB_OBSV_BV_02_C_2026_03_26_01_09_14.xml</t>
-  </si>
-  <si>
     <t>Observation procedure, Active Scanning</t>
   </si>
   <si>
@@ -334,9 +277,6 @@
     <t>GAP/CONN/ACEP/BV-01-C</t>
   </si>
   <si>
-    <t>GAP_CONN_ACEP_BV_01_C_2026_03_26_01_10_01.xml</t>
-  </si>
-  <si>
     <t>Auto Connection Establishment procedure, Directed Connectable mode</t>
   </si>
   <si>
@@ -349,9 +289,6 @@
     <t>GAP/CONN/UCON/BV-01-C</t>
   </si>
   <si>
-    <t>GAP_CONN_UCON_BV_01_C_2026_03_26_01_09_42.xml</t>
-  </si>
-  <si>
     <t>Undirected Connectable mode, Non-Discoverable mode</t>
   </si>
   <si>
@@ -364,9 +301,6 @@
     <t>GATT/CL/GAC/BV-01-C</t>
   </si>
   <si>
-    <t>GATT_CL_GAC_BV_01_C_2026_03_26_01_10_20.xml</t>
-  </si>
-  <si>
     <t>Server Configuration - by Client</t>
   </si>
   <si>
@@ -379,9 +313,6 @@
     <t>GATT/CL/GAN/BV-01-C</t>
   </si>
   <si>
-    <t>GATT_CL_GAN_BV_01_C_2026_03_26_01_11_48.xml</t>
-  </si>
-  <si>
     <t>Characteristic Value Notification - to Client</t>
   </si>
   <si>
@@ -394,9 +325,6 @@
     <t>GATT/CL/GAR/BV-01-C</t>
   </si>
   <si>
-    <t>GATT_CL_GAR_BV_01_C_2026_03_26_01_10_43.xml</t>
-  </si>
-  <si>
     <t>Read Characteristic Value - by Client</t>
   </si>
   <si>
@@ -409,9 +337,6 @@
     <t>GATT/CL/GAW/BV-01-C</t>
   </si>
   <si>
-    <t>GATT_CL_GAW_BV_01_C_2026_03_26_01_11_16.xml</t>
-  </si>
-  <si>
     <t>Write without Response - by Client</t>
   </si>
   <si>
@@ -424,9 +349,6 @@
     <t>GATT/SR/GAC/BV-01-C</t>
   </si>
   <si>
-    <t>GATT_SR_GAC_BV_01_C_2026_03_26_01_12_26.xml</t>
-  </si>
-  <si>
     <t>Server Configuration - of Server</t>
   </si>
   <si>
@@ -442,9 +364,6 @@
     <t>ERRATA ES-27410</t>
   </si>
   <si>
-    <t>GATT_SR_GAN_BV_01_C_2026_03_26_01_14_31.xml</t>
-  </si>
-  <si>
     <t>Characteristic Value Notification - by Server, no bonding</t>
   </si>
   <si>
@@ -457,9 +376,6 @@
     <t>GATT/SR/GAR/BV-01-C</t>
   </si>
   <si>
-    <t>GATT_SR_GAR_BV_01_C_2026_03_26_01_13_12.xml</t>
-  </si>
-  <si>
     <t>Read Characteristic Value - from Server</t>
   </si>
   <si>
@@ -472,9 +388,6 @@
     <t>GATT/SR/GAW/BV-01-C</t>
   </si>
   <si>
-    <t>GATT_SR_GAW_BV_01_C_2026_03_26_01_13_52.xml</t>
-  </si>
-  <si>
     <t>Write Without Response - to Server</t>
   </si>
   <si>
@@ -487,9 +400,6 @@
     <t>GMCS/SR/MCP/BV-01-C</t>
   </si>
   <si>
-    <t>GMCS_SR_MCP_BV_01_C_2026_03_26_01_27_48.xml</t>
-  </si>
-  <si>
     <t>Play from Paused</t>
   </si>
   <si>
@@ -514,9 +424,6 @@
     <t>HAP/HA/DISC/BV-01-C</t>
   </si>
   <si>
-    <t>HAP_HA_DISC_BV_01_C_2026_03_26_01_28_57.xml</t>
-  </si>
-  <si>
     <t>Sink Audio Locations Characteristic, Binaural</t>
   </si>
   <si>
@@ -529,9 +436,6 @@
     <t>HAS/SR/AI/BV-01-C</t>
   </si>
   <si>
-    <t>HAS_SR_AI_BV_01_C_2026_03_26_01_29_38.xml</t>
-  </si>
-  <si>
     <t>Active Preset Index Notifications</t>
   </si>
   <si>
@@ -544,9 +448,6 @@
     <t>IAS/SR/CW/BV-01-C</t>
   </si>
   <si>
-    <t>IAS_SR_CW_BV_01_C_2026_03_26_01_30_08.xml</t>
-  </si>
-  <si>
     <t>Characteristic Write Without Response - Alert Level</t>
   </si>
   <si>
@@ -559,9 +460,6 @@
     <t>L2CAP/ECFC/BV-01-C</t>
   </si>
   <si>
-    <t>L2CAP_ECFC_BV_01_C_2026_03_26_01_15_44.xml</t>
-  </si>
-  <si>
     <t>L2CAP Credit Based Connection Request - Legacy Peer, LE</t>
   </si>
   <si>
@@ -574,9 +472,6 @@
     <t>L2CAP/LE/CFC/BV-01-C</t>
   </si>
   <si>
-    <t>L2CAP_LE_CFC_BV_01_C_2026_03_26_01_15_27.xml</t>
-  </si>
-  <si>
     <t>LE Credit Based Connection Request - Legacy Peer</t>
   </si>
   <si>
@@ -589,9 +484,6 @@
     <t>MBTM/CL/BT/BV-01-C</t>
   </si>
   <si>
-    <t>MBTM_CL_BT_BV_01_C_2026_03_26_01_38_25.xml</t>
-  </si>
-  <si>
     <t>Transfer BLOB Procedure, Push BLOB Transfer Mode</t>
   </si>
   <si>
@@ -604,9 +496,6 @@
     <t>MBTM/SR/BT/BV-01-C</t>
   </si>
   <si>
-    <t>MBTM_SR_BT_BV_01_C_2026_03_26_01_37_29.xml</t>
-  </si>
-  <si>
     <t>Transfer Block Sequence, Push BLOB Transfer Mode</t>
   </si>
   <si>
@@ -619,9 +508,6 @@
     <t>MCP/CL/CGGIT/CHA/BV-02-C</t>
   </si>
   <si>
-    <t>MCP_CL_CGGIT_CHA_BV_02_C_2026_03_26_01_30_32.xml</t>
-  </si>
-  <si>
     <t>Characteristic GGIT - Media Player Icon Object ID</t>
   </si>
   <si>
@@ -634,9 +520,6 @@
     <t>MESH/CFGCL/CFG/AKL/BV-01-C</t>
   </si>
   <si>
-    <t>MESH_CFGCL_CFG_AKL_BV_01_C_2026_03_26_01_39_22.xml</t>
-  </si>
-  <si>
     <t>Send Config AppKey Add Messages</t>
   </si>
   <si>
@@ -649,9 +532,6 @@
     <t>MESH/NODE/BV-01-C</t>
   </si>
   <si>
-    <t>MESH_NODE_BV_01_C_2026_03_26_01_40_32.xml</t>
-  </si>
-  <si>
     <t>Provisioning and reprovisioning</t>
   </si>
   <si>
@@ -664,9 +544,6 @@
     <t>MESH/SR/BCM/BDS/BV-01-C</t>
   </si>
   <si>
-    <t>MESH_SR_BCM_BDS_BV_01_C_2026_03_26_01_39_55.xml</t>
-  </si>
-  <si>
     <t>Bridging Table State Add Behavior</t>
   </si>
   <si>
@@ -679,9 +556,6 @@
     <t>MICP/CL/CP/BV-01-C</t>
   </si>
   <si>
-    <t>MICP_CL_CP_BV_01_C_2026_03_26_01_31_03.xml</t>
-  </si>
-  <si>
     <t>2026-03-26 01:31:01</t>
   </si>
   <si>
@@ -691,9 +565,6 @@
     <t>MICS/SR/SGGIT/CHA/BV-01-C</t>
   </si>
   <si>
-    <t>MICS_SR_SGGIT_CHA_BV_01_C_2026_03_26_01_31_27.xml</t>
-  </si>
-  <si>
     <t>Characteristic GGIT - Mute</t>
   </si>
   <si>
@@ -706,9 +577,6 @@
     <t>OTS/SR/CON/BV-01-C</t>
   </si>
   <si>
-    <t>OTS_SR_CON_BV_01_C_2026_03_26_01_16_12.xml</t>
-  </si>
-  <si>
     <t>Configure Indication - OACP</t>
   </si>
   <si>
@@ -721,9 +589,6 @@
     <t>PACS/SR/PCU/BV-01-C</t>
   </si>
   <si>
-    <t>PACS_SR_PCU_BV_01_C_2026_03_26_01_31_53.xml</t>
-  </si>
-  <si>
     <t>Update Sink PAC - Connected Client</t>
   </si>
   <si>
@@ -736,9 +601,6 @@
     <t>PBP/PBS/STR/BV-01-C</t>
   </si>
   <si>
-    <t>PBP_PBS_STR_BV_01_C_2026_03_26_01_32_22.xml</t>
-  </si>
-  <si>
     <t>Standard Quality Streaming Support, 16_2_1 - PBS</t>
   </si>
   <si>
@@ -751,9 +613,6 @@
     <t>SM/CEN/JW/BV-01-C</t>
   </si>
   <si>
-    <t>SM_CEN_JW_BV_01_C_2026_03_26_01_16_40.xml</t>
-  </si>
-  <si>
     <t>Just Works IUT Initiator - Success</t>
   </si>
   <si>
@@ -766,9 +625,6 @@
     <t>SM/CEN/SCJW/BV-01-C</t>
   </si>
   <si>
-    <t>SM_CEN_SCJW_BV_01_C_2026_03_26_01_16_59.xml</t>
-  </si>
-  <si>
     <t>Just Works, IUT Initiator, Secure Connections - Success</t>
   </si>
   <si>
@@ -781,9 +637,6 @@
     <t>SM/PER/JW/BV-02-C</t>
   </si>
   <si>
-    <t>SM_PER_JW_BV_02_C_2026_03_26_01_17_28.xml</t>
-  </si>
-  <si>
     <t>Just Works IUT Responder - Success</t>
   </si>
   <si>
@@ -796,9 +649,6 @@
     <t>SM/PER/SCJW/BV-02-C</t>
   </si>
   <si>
-    <t>SM_PER_SCJW_BV_02_C_2026_03_26_01_17_49.xml</t>
-  </si>
-  <si>
     <t>Just Works, IUT Responder, Secure Connections - Success</t>
   </si>
   <si>
@@ -811,9 +661,6 @@
     <t>TBS/SR/CP/BV-01-C</t>
   </si>
   <si>
-    <t>TBS_SR_CP_BV_01_C_2026_03_26_01_32_48.xml</t>
-  </si>
-  <si>
     <t>2026-03-26 01:32:46</t>
   </si>
   <si>
@@ -823,9 +670,6 @@
     <t>TMAP/BMR/ASC/BV-03-C</t>
   </si>
   <si>
-    <t>TMAP_BMR_ASC_BV_03_C_2026_03_26_01_33_30.xml</t>
-  </si>
-  <si>
     <t>BMR Audio Location Front Left</t>
   </si>
   <si>
@@ -838,9 +682,6 @@
     <t>VCP/VC/AICP/BV-01-C</t>
   </si>
   <si>
-    <t>VCP_VC_AICP_BV_01_C_2026_03_26_01_33_45.xml</t>
-  </si>
-  <si>
     <t>2026-03-26 01:33:43</t>
   </si>
   <si>
@@ -850,9 +691,6 @@
     <t>VCS/SR/SGGIT/CHA/BV-01-C</t>
   </si>
   <si>
-    <t>VCS_SR_SGGIT_CHA_BV_01_C_2026_03_26_01_34_10.xml</t>
-  </si>
-  <si>
     <t>Characteristic GGIT - Volume State</t>
   </si>
   <si>
@@ -863,9 +701,6 @@
   </si>
   <si>
     <t>VOCS/SR/CP/BV-01-C</t>
-  </si>
-  <si>
-    <t>VOCS_SR_CP_BV_01_C_2026_03_26_01_34_40.xml</t>
   </si>
   <si>
     <t>Set Volume Offset</t>
@@ -1379,7 +1214,7 @@
         <v>8</v>
       </c>
       <c r="K3" t="s">
-        <v>287</v>
+        <v>232</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -1389,17 +1224,14 @@
       <c r="B4" t="s">
         <v>10</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>11</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>12</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>13</v>
-      </c>
-      <c r="G4" t="s">
-        <v>14</v>
       </c>
       <c r="H4">
         <v>89.45999999999999</v>
@@ -1413,22 +1245,19 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" t="s">
         <v>15</v>
       </c>
-      <c r="B5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="F5" t="s">
         <v>16</v>
       </c>
-      <c r="E5" t="s">
+      <c r="G5" t="s">
         <v>17</v>
-      </c>
-      <c r="F5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G5" t="s">
-        <v>19</v>
       </c>
       <c r="H5">
         <v>27.06</v>
@@ -1436,80 +1265,71 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" t="s">
         <v>20</v>
       </c>
-      <c r="B6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="G6" t="s">
         <v>21</v>
-      </c>
-      <c r="E6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6" t="s">
-        <v>23</v>
-      </c>
-      <c r="G6" t="s">
-        <v>24</v>
       </c>
       <c r="H6">
         <v>31.37</v>
       </c>
       <c r="K6" t="s">
-        <v>288</v>
+        <v>233</v>
       </c>
       <c r="L6" t="s">
-        <v>289</v>
+        <v>234</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" t="s">
+        <v>24</v>
+      </c>
+      <c r="G7" t="s">
         <v>25</v>
-      </c>
-      <c r="B7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" t="s">
-        <v>26</v>
-      </c>
-      <c r="E7" t="s">
-        <v>27</v>
-      </c>
-      <c r="F7" t="s">
-        <v>28</v>
-      </c>
-      <c r="G7" t="s">
-        <v>29</v>
       </c>
       <c r="H7">
         <v>14.54</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>290</v>
+        <v>235</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>291</v>
+        <v>236</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B8" t="s">
         <v>10</v>
       </c>
-      <c r="D8" t="s">
-        <v>31</v>
-      </c>
       <c r="E8" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F8" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G8" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="H8">
         <v>17.48</v>
@@ -1517,22 +1337,19 @@
     </row>
     <row r="9" spans="1:12">
       <c r="A9" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B9" t="s">
         <v>10</v>
       </c>
-      <c r="D9" t="s">
-        <v>36</v>
-      </c>
       <c r="E9" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="F9" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="G9" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="H9">
         <v>23.06</v>
@@ -1540,22 +1357,19 @@
     </row>
     <row r="10" spans="1:12">
       <c r="A10" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B10" t="s">
         <v>10</v>
       </c>
-      <c r="D10" t="s">
-        <v>41</v>
-      </c>
       <c r="E10" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="F10" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="G10" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="H10">
         <v>46.47</v>
@@ -1563,22 +1377,19 @@
     </row>
     <row r="11" spans="1:12">
       <c r="A11" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B11" t="s">
         <v>10</v>
       </c>
-      <c r="D11" t="s">
-        <v>46</v>
-      </c>
       <c r="E11" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="F11" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="G11" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="H11">
         <v>21.73</v>
@@ -1586,22 +1397,19 @@
     </row>
     <row r="12" spans="1:12">
       <c r="A12" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="B12" t="s">
         <v>10</v>
       </c>
-      <c r="D12" t="s">
-        <v>51</v>
-      </c>
       <c r="E12" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="F12" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="G12" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="H12">
         <v>22.12</v>
@@ -1609,22 +1417,19 @@
     </row>
     <row r="13" spans="1:12">
       <c r="A13" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="B13" t="s">
         <v>10</v>
       </c>
-      <c r="D13" t="s">
-        <v>56</v>
-      </c>
       <c r="E13" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="F13" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="G13" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="H13">
         <v>38.78</v>
@@ -1632,22 +1437,19 @@
     </row>
     <row r="14" spans="1:12">
       <c r="A14" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="B14" t="s">
         <v>10</v>
       </c>
-      <c r="D14" t="s">
-        <v>61</v>
-      </c>
       <c r="E14" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F14" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="G14" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="H14">
         <v>18.42</v>
@@ -1655,22 +1457,19 @@
     </row>
     <row r="15" spans="1:12">
       <c r="A15" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="B15" t="s">
         <v>10</v>
       </c>
-      <c r="D15" t="s">
-        <v>66</v>
-      </c>
       <c r="E15" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="F15" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="G15" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="H15">
         <v>64</v>
@@ -1678,22 +1477,19 @@
     </row>
     <row r="16" spans="1:12">
       <c r="A16" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="B16" t="s">
         <v>10</v>
       </c>
-      <c r="D16" t="s">
-        <v>71</v>
-      </c>
       <c r="E16" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="F16" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="G16" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="H16">
         <v>41.16</v>
@@ -1701,22 +1497,19 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="B17" t="s">
         <v>10</v>
       </c>
-      <c r="D17" t="s">
-        <v>76</v>
-      </c>
       <c r="E17" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="F17" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="G17" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="H17">
         <v>24.45</v>
@@ -1724,22 +1517,19 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="B18" t="s">
         <v>10</v>
       </c>
-      <c r="D18" t="s">
-        <v>81</v>
-      </c>
       <c r="E18" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="F18" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="G18" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="H18">
         <v>24.11</v>
@@ -1747,22 +1537,19 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="B19" t="s">
         <v>10</v>
       </c>
-      <c r="D19" t="s">
-        <v>86</v>
-      </c>
       <c r="E19" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="F19" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="G19" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="H19">
         <v>35.3</v>
@@ -1770,22 +1557,19 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="B20" t="s">
         <v>10</v>
       </c>
-      <c r="D20" t="s">
-        <v>91</v>
-      </c>
       <c r="E20" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="F20" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="G20" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="H20">
         <v>31.24</v>
@@ -1793,22 +1577,19 @@
     </row>
     <row r="21" spans="1:8">
       <c r="A21" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="B21" t="s">
         <v>10</v>
       </c>
-      <c r="D21" t="s">
-        <v>96</v>
-      </c>
       <c r="E21" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="F21" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="G21" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="H21">
         <v>22.76</v>
@@ -1816,22 +1597,19 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="B22" t="s">
         <v>10</v>
       </c>
-      <c r="D22" t="s">
-        <v>101</v>
-      </c>
       <c r="E22" t="s">
-        <v>102</v>
+        <v>83</v>
       </c>
       <c r="F22" t="s">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="G22" t="s">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="H22">
         <v>25.59</v>
@@ -1839,22 +1617,19 @@
     </row>
     <row r="23" spans="1:8">
       <c r="A23" t="s">
-        <v>105</v>
+        <v>86</v>
       </c>
       <c r="B23" t="s">
         <v>10</v>
       </c>
-      <c r="D23" t="s">
-        <v>106</v>
-      </c>
       <c r="E23" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="F23" t="s">
-        <v>108</v>
+        <v>88</v>
       </c>
       <c r="G23" t="s">
-        <v>109</v>
+        <v>89</v>
       </c>
       <c r="H23">
         <v>16.86</v>
@@ -1862,22 +1637,19 @@
     </row>
     <row r="24" spans="1:8">
       <c r="A24" t="s">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="B24" t="s">
         <v>10</v>
       </c>
-      <c r="D24" t="s">
-        <v>111</v>
-      </c>
       <c r="E24" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="F24" t="s">
-        <v>113</v>
+        <v>92</v>
       </c>
       <c r="G24" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="H24">
         <v>16.36</v>
@@ -1885,22 +1657,19 @@
     </row>
     <row r="25" spans="1:8">
       <c r="A25" t="s">
-        <v>115</v>
+        <v>94</v>
       </c>
       <c r="B25" t="s">
         <v>10</v>
       </c>
-      <c r="D25" t="s">
-        <v>116</v>
-      </c>
       <c r="E25" t="s">
-        <v>117</v>
+        <v>95</v>
       </c>
       <c r="F25" t="s">
-        <v>118</v>
+        <v>96</v>
       </c>
       <c r="G25" t="s">
-        <v>119</v>
+        <v>97</v>
       </c>
       <c r="H25">
         <v>21.16</v>
@@ -1908,22 +1677,19 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26" t="s">
-        <v>120</v>
+        <v>98</v>
       </c>
       <c r="B26" t="s">
         <v>10</v>
       </c>
-      <c r="D26" t="s">
-        <v>121</v>
-      </c>
       <c r="E26" t="s">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="F26" t="s">
-        <v>123</v>
+        <v>100</v>
       </c>
       <c r="G26" t="s">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="H26">
         <v>33.63</v>
@@ -1931,22 +1697,19 @@
     </row>
     <row r="27" spans="1:8">
       <c r="A27" t="s">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="B27" t="s">
         <v>10</v>
       </c>
-      <c r="D27" t="s">
-        <v>126</v>
-      </c>
       <c r="E27" t="s">
-        <v>127</v>
+        <v>103</v>
       </c>
       <c r="F27" t="s">
-        <v>128</v>
+        <v>104</v>
       </c>
       <c r="G27" t="s">
-        <v>129</v>
+        <v>105</v>
       </c>
       <c r="H27">
         <v>31.24</v>
@@ -1954,22 +1717,19 @@
     </row>
     <row r="28" spans="1:8">
       <c r="A28" t="s">
-        <v>130</v>
+        <v>106</v>
       </c>
       <c r="B28" t="s">
         <v>10</v>
       </c>
-      <c r="D28" t="s">
-        <v>131</v>
-      </c>
       <c r="E28" t="s">
-        <v>132</v>
+        <v>107</v>
       </c>
       <c r="F28" t="s">
-        <v>133</v>
+        <v>108</v>
       </c>
       <c r="G28" t="s">
-        <v>134</v>
+        <v>109</v>
       </c>
       <c r="H28">
         <v>30.21</v>
@@ -1977,22 +1737,19 @@
     </row>
     <row r="29" spans="1:8">
       <c r="A29" t="s">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="B29" t="s">
         <v>10</v>
       </c>
-      <c r="D29" t="s">
-        <v>136</v>
-      </c>
       <c r="E29" t="s">
-        <v>137</v>
+        <v>111</v>
       </c>
       <c r="F29" t="s">
-        <v>138</v>
+        <v>112</v>
       </c>
       <c r="G29" t="s">
-        <v>139</v>
+        <v>113</v>
       </c>
       <c r="H29">
         <v>43.83</v>
@@ -2000,25 +1757,22 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30" t="s">
-        <v>140</v>
+        <v>114</v>
       </c>
       <c r="B30" t="s">
         <v>10</v>
       </c>
       <c r="C30" t="s">
-        <v>141</v>
-      </c>
-      <c r="D30" t="s">
-        <v>142</v>
+        <v>115</v>
       </c>
       <c r="E30" t="s">
-        <v>143</v>
+        <v>116</v>
       </c>
       <c r="F30" t="s">
-        <v>144</v>
+        <v>117</v>
       </c>
       <c r="G30" t="s">
-        <v>145</v>
+        <v>118</v>
       </c>
       <c r="H30">
         <v>57</v>
@@ -2026,22 +1780,19 @@
     </row>
     <row r="31" spans="1:8">
       <c r="A31" t="s">
-        <v>146</v>
+        <v>119</v>
       </c>
       <c r="B31" t="s">
         <v>10</v>
       </c>
-      <c r="D31" t="s">
-        <v>147</v>
-      </c>
       <c r="E31" t="s">
-        <v>148</v>
+        <v>120</v>
       </c>
       <c r="F31" t="s">
-        <v>149</v>
+        <v>121</v>
       </c>
       <c r="G31" t="s">
-        <v>150</v>
+        <v>122</v>
       </c>
       <c r="H31">
         <v>37.67</v>
@@ -2049,22 +1800,19 @@
     </row>
     <row r="32" spans="1:8">
       <c r="A32" t="s">
-        <v>151</v>
+        <v>123</v>
       </c>
       <c r="B32" t="s">
         <v>10</v>
       </c>
-      <c r="D32" t="s">
-        <v>152</v>
-      </c>
       <c r="E32" t="s">
-        <v>153</v>
+        <v>124</v>
       </c>
       <c r="F32" t="s">
-        <v>154</v>
+        <v>125</v>
       </c>
       <c r="G32" t="s">
-        <v>155</v>
+        <v>126</v>
       </c>
       <c r="H32">
         <v>37.45</v>
@@ -2072,22 +1820,19 @@
     </row>
     <row r="33" spans="1:8">
       <c r="A33" t="s">
-        <v>156</v>
+        <v>127</v>
       </c>
       <c r="B33" t="s">
         <v>10</v>
       </c>
-      <c r="D33" t="s">
-        <v>157</v>
-      </c>
       <c r="E33" t="s">
-        <v>158</v>
+        <v>128</v>
       </c>
       <c r="F33" t="s">
-        <v>159</v>
+        <v>129</v>
       </c>
       <c r="G33" t="s">
-        <v>160</v>
+        <v>130</v>
       </c>
       <c r="H33">
         <v>27.29</v>
@@ -2095,19 +1840,19 @@
     </row>
     <row r="34" spans="1:8">
       <c r="A34" t="s">
-        <v>161</v>
+        <v>131</v>
       </c>
       <c r="B34" t="s">
         <v>10</v>
       </c>
       <c r="E34" t="s">
-        <v>162</v>
+        <v>132</v>
       </c>
       <c r="F34" t="s">
-        <v>163</v>
+        <v>133</v>
       </c>
       <c r="G34" t="s">
-        <v>164</v>
+        <v>134</v>
       </c>
       <c r="H34">
         <v>37.66</v>
@@ -2115,22 +1860,19 @@
     </row>
     <row r="35" spans="1:8">
       <c r="A35" t="s">
-        <v>165</v>
+        <v>135</v>
       </c>
       <c r="B35" t="s">
         <v>10</v>
       </c>
-      <c r="D35" t="s">
-        <v>166</v>
-      </c>
       <c r="E35" t="s">
-        <v>167</v>
+        <v>136</v>
       </c>
       <c r="F35" t="s">
-        <v>168</v>
+        <v>137</v>
       </c>
       <c r="G35" t="s">
-        <v>169</v>
+        <v>138</v>
       </c>
       <c r="H35">
         <v>39.82</v>
@@ -2138,22 +1880,19 @@
     </row>
     <row r="36" spans="1:8">
       <c r="A36" t="s">
-        <v>170</v>
+        <v>139</v>
       </c>
       <c r="B36" t="s">
         <v>10</v>
       </c>
-      <c r="D36" t="s">
-        <v>171</v>
-      </c>
       <c r="E36" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="F36" t="s">
-        <v>173</v>
+        <v>141</v>
       </c>
       <c r="G36" t="s">
-        <v>174</v>
+        <v>142</v>
       </c>
       <c r="H36">
         <v>28.5</v>
@@ -2161,22 +1900,19 @@
     </row>
     <row r="37" spans="1:8">
       <c r="A37" t="s">
-        <v>175</v>
+        <v>143</v>
       </c>
       <c r="B37" t="s">
         <v>10</v>
       </c>
-      <c r="D37" t="s">
-        <v>176</v>
-      </c>
       <c r="E37" t="s">
-        <v>177</v>
+        <v>144</v>
       </c>
       <c r="F37" t="s">
-        <v>178</v>
+        <v>145</v>
       </c>
       <c r="G37" t="s">
-        <v>179</v>
+        <v>146</v>
       </c>
       <c r="H37">
         <v>21.54</v>
@@ -2184,22 +1920,19 @@
     </row>
     <row r="38" spans="1:8">
       <c r="A38" t="s">
-        <v>180</v>
+        <v>147</v>
       </c>
       <c r="B38" t="s">
         <v>10</v>
       </c>
-      <c r="D38" t="s">
-        <v>181</v>
-      </c>
       <c r="E38" t="s">
-        <v>182</v>
+        <v>148</v>
       </c>
       <c r="F38" t="s">
-        <v>183</v>
+        <v>149</v>
       </c>
       <c r="G38" t="s">
-        <v>184</v>
+        <v>150</v>
       </c>
       <c r="H38">
         <v>25.39</v>
@@ -2207,22 +1940,19 @@
     </row>
     <row r="39" spans="1:8">
       <c r="A39" t="s">
-        <v>185</v>
+        <v>151</v>
       </c>
       <c r="B39" t="s">
         <v>10</v>
       </c>
-      <c r="D39" t="s">
-        <v>186</v>
-      </c>
       <c r="E39" t="s">
-        <v>187</v>
+        <v>152</v>
       </c>
       <c r="F39" t="s">
-        <v>188</v>
+        <v>153</v>
       </c>
       <c r="G39" t="s">
-        <v>189</v>
+        <v>154</v>
       </c>
       <c r="H39">
         <v>14.86</v>
@@ -2230,22 +1960,19 @@
     </row>
     <row r="40" spans="1:8">
       <c r="A40" t="s">
-        <v>190</v>
+        <v>155</v>
       </c>
       <c r="B40" t="s">
         <v>10</v>
       </c>
-      <c r="D40" t="s">
-        <v>191</v>
-      </c>
       <c r="E40" t="s">
-        <v>192</v>
+        <v>156</v>
       </c>
       <c r="F40" t="s">
-        <v>193</v>
+        <v>157</v>
       </c>
       <c r="G40" t="s">
-        <v>194</v>
+        <v>158</v>
       </c>
       <c r="H40">
         <v>42.14</v>
@@ -2253,22 +1980,19 @@
     </row>
     <row r="41" spans="1:8">
       <c r="A41" t="s">
-        <v>195</v>
+        <v>159</v>
       </c>
       <c r="B41" t="s">
         <v>10</v>
       </c>
-      <c r="D41" t="s">
-        <v>196</v>
-      </c>
       <c r="E41" t="s">
-        <v>197</v>
+        <v>160</v>
       </c>
       <c r="F41" t="s">
-        <v>198</v>
+        <v>161</v>
       </c>
       <c r="G41" t="s">
-        <v>199</v>
+        <v>162</v>
       </c>
       <c r="H41">
         <v>40.38</v>
@@ -2276,22 +2000,19 @@
     </row>
     <row r="42" spans="1:8">
       <c r="A42" t="s">
-        <v>200</v>
+        <v>163</v>
       </c>
       <c r="B42" t="s">
         <v>10</v>
       </c>
-      <c r="D42" t="s">
-        <v>201</v>
-      </c>
       <c r="E42" t="s">
-        <v>202</v>
+        <v>164</v>
       </c>
       <c r="F42" t="s">
-        <v>203</v>
+        <v>165</v>
       </c>
       <c r="G42" t="s">
-        <v>204</v>
+        <v>166</v>
       </c>
       <c r="H42">
         <v>28.86</v>
@@ -2299,22 +2020,19 @@
     </row>
     <row r="43" spans="1:8">
       <c r="A43" t="s">
-        <v>205</v>
+        <v>167</v>
       </c>
       <c r="B43" t="s">
         <v>10</v>
       </c>
-      <c r="D43" t="s">
-        <v>206</v>
-      </c>
       <c r="E43" t="s">
-        <v>207</v>
+        <v>168</v>
       </c>
       <c r="F43" t="s">
-        <v>208</v>
+        <v>169</v>
       </c>
       <c r="G43" t="s">
-        <v>209</v>
+        <v>170</v>
       </c>
       <c r="H43">
         <v>30.63</v>
@@ -2322,22 +2040,19 @@
     </row>
     <row r="44" spans="1:8">
       <c r="A44" t="s">
-        <v>210</v>
+        <v>171</v>
       </c>
       <c r="B44" t="s">
         <v>10</v>
       </c>
-      <c r="D44" t="s">
-        <v>211</v>
-      </c>
       <c r="E44" t="s">
-        <v>212</v>
+        <v>172</v>
       </c>
       <c r="F44" t="s">
-        <v>213</v>
+        <v>173</v>
       </c>
       <c r="G44" t="s">
-        <v>214</v>
+        <v>174</v>
       </c>
       <c r="H44">
         <v>31.18</v>
@@ -2345,22 +2060,19 @@
     </row>
     <row r="45" spans="1:8">
       <c r="A45" t="s">
-        <v>215</v>
+        <v>175</v>
       </c>
       <c r="B45" t="s">
         <v>10</v>
       </c>
-      <c r="D45" t="s">
-        <v>216</v>
-      </c>
       <c r="E45" t="s">
-        <v>217</v>
+        <v>176</v>
       </c>
       <c r="F45" t="s">
-        <v>218</v>
+        <v>177</v>
       </c>
       <c r="G45" t="s">
-        <v>219</v>
+        <v>178</v>
       </c>
       <c r="H45">
         <v>34.95</v>
@@ -2368,22 +2080,19 @@
     </row>
     <row r="46" spans="1:8">
       <c r="A46" t="s">
-        <v>220</v>
+        <v>179</v>
       </c>
       <c r="B46" t="s">
         <v>10</v>
       </c>
-      <c r="D46" t="s">
-        <v>221</v>
-      </c>
       <c r="E46" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F46" t="s">
-        <v>222</v>
+        <v>180</v>
       </c>
       <c r="G46" t="s">
-        <v>223</v>
+        <v>181</v>
       </c>
       <c r="H46">
         <v>21.77</v>
@@ -2391,22 +2100,19 @@
     </row>
     <row r="47" spans="1:8">
       <c r="A47" t="s">
-        <v>224</v>
+        <v>182</v>
       </c>
       <c r="B47" t="s">
         <v>10</v>
       </c>
-      <c r="D47" t="s">
-        <v>225</v>
-      </c>
       <c r="E47" t="s">
-        <v>226</v>
+        <v>183</v>
       </c>
       <c r="F47" t="s">
-        <v>227</v>
+        <v>184</v>
       </c>
       <c r="G47" t="s">
-        <v>228</v>
+        <v>185</v>
       </c>
       <c r="H47">
         <v>24.98</v>
@@ -2414,22 +2120,19 @@
     </row>
     <row r="48" spans="1:8">
       <c r="A48" t="s">
-        <v>229</v>
+        <v>186</v>
       </c>
       <c r="B48" t="s">
         <v>10</v>
       </c>
-      <c r="D48" t="s">
-        <v>230</v>
-      </c>
       <c r="E48" t="s">
-        <v>231</v>
+        <v>187</v>
       </c>
       <c r="F48" t="s">
-        <v>232</v>
+        <v>188</v>
       </c>
       <c r="G48" t="s">
-        <v>233</v>
+        <v>189</v>
       </c>
       <c r="H48">
         <v>24.41</v>
@@ -2437,22 +2140,19 @@
     </row>
     <row r="49" spans="1:8">
       <c r="A49" t="s">
-        <v>234</v>
+        <v>190</v>
       </c>
       <c r="B49" t="s">
         <v>10</v>
       </c>
-      <c r="D49" t="s">
-        <v>235</v>
-      </c>
       <c r="E49" t="s">
-        <v>236</v>
+        <v>191</v>
       </c>
       <c r="F49" t="s">
-        <v>237</v>
+        <v>192</v>
       </c>
       <c r="G49" t="s">
-        <v>238</v>
+        <v>193</v>
       </c>
       <c r="H49">
         <v>26.19</v>
@@ -2460,22 +2160,19 @@
     </row>
     <row r="50" spans="1:8">
       <c r="A50" t="s">
-        <v>239</v>
+        <v>194</v>
       </c>
       <c r="B50" t="s">
         <v>10</v>
       </c>
-      <c r="D50" t="s">
-        <v>240</v>
-      </c>
       <c r="E50" t="s">
-        <v>241</v>
+        <v>195</v>
       </c>
       <c r="F50" t="s">
-        <v>242</v>
+        <v>196</v>
       </c>
       <c r="G50" t="s">
-        <v>243</v>
+        <v>197</v>
       </c>
       <c r="H50">
         <v>23.98</v>
@@ -2483,22 +2180,19 @@
     </row>
     <row r="51" spans="1:8">
       <c r="A51" t="s">
-        <v>244</v>
+        <v>198</v>
       </c>
       <c r="B51" t="s">
         <v>10</v>
       </c>
-      <c r="D51" t="s">
-        <v>245</v>
-      </c>
       <c r="E51" t="s">
-        <v>246</v>
+        <v>199</v>
       </c>
       <c r="F51" t="s">
-        <v>247</v>
+        <v>200</v>
       </c>
       <c r="G51" t="s">
-        <v>248</v>
+        <v>201</v>
       </c>
       <c r="H51">
         <v>17.03</v>
@@ -2506,22 +2200,19 @@
     </row>
     <row r="52" spans="1:8">
       <c r="A52" t="s">
-        <v>249</v>
+        <v>202</v>
       </c>
       <c r="B52" t="s">
         <v>10</v>
       </c>
-      <c r="D52" t="s">
-        <v>250</v>
-      </c>
       <c r="E52" t="s">
-        <v>251</v>
+        <v>203</v>
       </c>
       <c r="F52" t="s">
-        <v>252</v>
+        <v>204</v>
       </c>
       <c r="G52" t="s">
-        <v>253</v>
+        <v>205</v>
       </c>
       <c r="H52">
         <v>26.49</v>
@@ -2529,22 +2220,19 @@
     </row>
     <row r="53" spans="1:8">
       <c r="A53" t="s">
-        <v>254</v>
+        <v>206</v>
       </c>
       <c r="B53" t="s">
         <v>10</v>
       </c>
-      <c r="D53" t="s">
-        <v>255</v>
-      </c>
       <c r="E53" t="s">
-        <v>256</v>
+        <v>207</v>
       </c>
       <c r="F53" t="s">
-        <v>257</v>
+        <v>208</v>
       </c>
       <c r="G53" t="s">
-        <v>258</v>
+        <v>209</v>
       </c>
       <c r="H53">
         <v>18.85</v>
@@ -2552,22 +2240,19 @@
     </row>
     <row r="54" spans="1:8">
       <c r="A54" t="s">
-        <v>259</v>
+        <v>210</v>
       </c>
       <c r="B54" t="s">
         <v>10</v>
       </c>
-      <c r="D54" t="s">
-        <v>260</v>
-      </c>
       <c r="E54" t="s">
-        <v>261</v>
+        <v>211</v>
       </c>
       <c r="F54" t="s">
-        <v>262</v>
+        <v>212</v>
       </c>
       <c r="G54" t="s">
-        <v>263</v>
+        <v>213</v>
       </c>
       <c r="H54">
         <v>33.44</v>
@@ -2575,22 +2260,19 @@
     </row>
     <row r="55" spans="1:8">
       <c r="A55" t="s">
-        <v>264</v>
+        <v>214</v>
       </c>
       <c r="B55" t="s">
         <v>10</v>
       </c>
-      <c r="D55" t="s">
-        <v>265</v>
-      </c>
       <c r="E55" t="s">
-        <v>162</v>
+        <v>132</v>
       </c>
       <c r="F55" t="s">
-        <v>266</v>
+        <v>215</v>
       </c>
       <c r="G55" t="s">
-        <v>267</v>
+        <v>216</v>
       </c>
       <c r="H55">
         <v>38.64</v>
@@ -2598,22 +2280,19 @@
     </row>
     <row r="56" spans="1:8">
       <c r="A56" t="s">
-        <v>268</v>
+        <v>217</v>
       </c>
       <c r="B56" t="s">
         <v>10</v>
       </c>
-      <c r="D56" t="s">
-        <v>269</v>
-      </c>
       <c r="E56" t="s">
-        <v>270</v>
+        <v>218</v>
       </c>
       <c r="F56" t="s">
-        <v>271</v>
+        <v>219</v>
       </c>
       <c r="G56" t="s">
-        <v>272</v>
+        <v>220</v>
       </c>
       <c r="H56">
         <v>15.01</v>
@@ -2621,22 +2300,19 @@
     </row>
     <row r="57" spans="1:8">
       <c r="A57" t="s">
-        <v>273</v>
+        <v>221</v>
       </c>
       <c r="B57" t="s">
         <v>10</v>
       </c>
-      <c r="D57" t="s">
-        <v>274</v>
-      </c>
       <c r="E57" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F57" t="s">
-        <v>275</v>
+        <v>222</v>
       </c>
       <c r="G57" t="s">
-        <v>276</v>
+        <v>223</v>
       </c>
       <c r="H57">
         <v>23.71</v>
@@ -2644,22 +2320,19 @@
     </row>
     <row r="58" spans="1:8">
       <c r="A58" t="s">
-        <v>277</v>
+        <v>224</v>
       </c>
       <c r="B58" t="s">
         <v>10</v>
       </c>
-      <c r="D58" t="s">
-        <v>278</v>
-      </c>
       <c r="E58" t="s">
-        <v>279</v>
+        <v>225</v>
       </c>
       <c r="F58" t="s">
-        <v>280</v>
+        <v>226</v>
       </c>
       <c r="G58" t="s">
-        <v>281</v>
+        <v>227</v>
       </c>
       <c r="H58">
         <v>27.93</v>
@@ -2667,22 +2340,19 @@
     </row>
     <row r="59" spans="1:8">
       <c r="A59" t="s">
-        <v>282</v>
+        <v>228</v>
       </c>
       <c r="B59" t="s">
         <v>10</v>
       </c>
-      <c r="D59" t="s">
-        <v>283</v>
-      </c>
       <c r="E59" t="s">
-        <v>284</v>
+        <v>229</v>
       </c>
       <c r="F59" t="s">
-        <v>285</v>
+        <v>230</v>
       </c>
       <c r="G59" t="s">
-        <v>286</v>
+        <v>231</v>
       </c>
       <c r="H59">
         <v>82.13</v>
